--- a/ig/main/CodeSystem-terminologie-cisis.xlsx
+++ b/ig/main/CodeSystem-terminologie-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202609160000</t>
+    <t>202609211638</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,13 +61,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T09:43:39-00:00</t>
+    <t>2026-09-21T16:38:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1816,7 +1816,7 @@
     <t>GEN-149</t>
   </si>
   <si>
-    <t>Communiquer : proches</t>
+    <t>Communiquer : proches</t>
   </si>
   <si>
     <t>GEN-150</t>
@@ -2449,13 +2449,13 @@
     <t>GEN-257</t>
   </si>
   <si>
-    <t>Bas grade (bien ou moyennement différencié)</t>
+    <t>Bas grade (bien ou moyennement différencié)</t>
   </si>
   <si>
     <t>GEN-258</t>
   </si>
   <si>
-    <t>Haut grade (peu différencié ou indifférencié)</t>
+    <t>Haut grade (peu différencié ou indifférencié)</t>
   </si>
   <si>
     <t>GEN-259</t>
@@ -3472,7 +3472,7 @@
     <t>GEN-428</t>
   </si>
   <si>
-    <t>Souhaitez-vous recevoir des kits pour prélèvements et envois d’échantillons de salive au CNR (recherche d’IgM/PCR) ?</t>
+    <t>Souhaitez-vous recevoir des kits pour prélèvements et envois d’échantillons de salive au CNR (recherche d’IgM/PCR) ?</t>
   </si>
   <si>
     <t>GEN-429</t>
@@ -4966,7 +4966,7 @@
     <t>MED-250</t>
   </si>
   <si>
-    <t>Proposition d’inclusion dans un essai clinique</t>
+    <t>Proposition d’inclusion dans un essai clinique</t>
   </si>
   <si>
     <t>MED-251</t>
@@ -7261,25 +7261,25 @@
     <t>MED-634</t>
   </si>
   <si>
-    <t>Classe 1 : toute la luette et les loges amygdaliennes sont visibles</t>
+    <t>Classe 1 : toute la luette et les loges amygdaliennes sont visibles</t>
   </si>
   <si>
     <t>MED-635</t>
   </si>
   <si>
-    <t>Classe 2 : la luette est partiellement visible</t>
+    <t>Classe 2 : la luette est partiellement visible</t>
   </si>
   <si>
     <t>MED-636</t>
   </si>
   <si>
-    <t>Classe 3 : le palais membraneux est visible</t>
+    <t>Classe 3 : le palais membraneux est visible</t>
   </si>
   <si>
     <t>MED-637</t>
   </si>
   <si>
-    <t>Classe 4 : seul le palais osseux est visible</t>
+    <t>Classe 4 : seul le palais osseux est visible</t>
   </si>
   <si>
     <t>MED-638</t>
@@ -7303,37 +7303,37 @@
     <t>MED-641</t>
   </si>
   <si>
-    <t>5,5</t>
+    <t>5.5</t>
   </si>
   <si>
     <t>MED-642</t>
   </si>
   <si>
-    <t>6</t>
+    <t>6.0</t>
   </si>
   <si>
     <t>MED-643</t>
   </si>
   <si>
-    <t>6,5</t>
+    <t>6.5</t>
   </si>
   <si>
     <t>MED-644</t>
   </si>
   <si>
-    <t>7</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>MED-645</t>
   </si>
   <si>
-    <t>7,5</t>
+    <t>7.5</t>
   </si>
   <si>
     <t>MED-646</t>
   </si>
   <si>
-    <t>8</t>
+    <t>8.0</t>
   </si>
   <si>
     <t>MED-647</t>
@@ -7663,7 +7663,7 @@
     <t>MED-710</t>
   </si>
   <si>
-    <t>Adénocarcinome 'adenoma-like'</t>
+    <t>Adénocarcinome "adenoma-like"</t>
   </si>
   <si>
     <t>MED-711</t>
@@ -7834,25 +7834,25 @@
     <t>MED-739</t>
   </si>
   <si>
-    <t>TRG0 : réponse complète - absence de cellules tumorale viables</t>
+    <t>TRG0 : réponse complète - absence de cellules tumorale viables</t>
   </si>
   <si>
     <t>MED-740</t>
   </si>
   <si>
-    <t>TRG1 : réponse modérée - cellules tumorales isolées ou rares petits amas de cellules tumorales</t>
+    <t>TRG1 : réponse modérée - cellules tumorales isolées ou rares petits amas de cellules tumorales</t>
   </si>
   <si>
     <t>MED-741</t>
   </si>
   <si>
-    <t>TRG2 : réponse minime - cancer avec régression tumorale évidente, mais persistance de plus que des cellules tumorales isolées ou de rares petits amas de cellules tumorales</t>
+    <t>TRG2 : réponse minime - cancer avec régression tumorale évidente, mais persistance de plus que des cellules tumorales isolées ou de rares petits amas de cellules tumorales</t>
   </si>
   <si>
     <t>MED-742</t>
   </si>
   <si>
-    <t>TRG3 : absence de réponse - pas d’aspect de régression tumorale</t>
+    <t>TRG3 : absence de réponse - pas d’aspect de régression tumorale</t>
   </si>
   <si>
     <t>MED-743</t>
@@ -10975,7 +10975,7 @@
     <t>MED-1277</t>
   </si>
   <si>
-    <t>Protocole de soins ALD patient</t>
+    <t>Protocole de soins ALD patient</t>
   </si>
   <si>
     <t>MED-1278</t>
@@ -11239,13 +11239,13 @@
     <t>MED-1323</t>
   </si>
   <si>
-    <t>Intervention d'un accompagnant éducatif et social</t>
+    <t>Intervention d'un accompagnant éducatif et social</t>
   </si>
   <si>
     <t>MED-1324</t>
   </si>
   <si>
-    <t>Intervention d'un infirmier d'un centre de santé infirmier</t>
+    <t>Intervention d'un infirmier d'un centre de santé infirmier</t>
   </si>
   <si>
     <t>MED-1325</t>
@@ -12784,7 +12784,7 @@
     <t>ORG-229</t>
   </si>
   <si>
-    <t>Provenance inconnue</t>
+    <t>Provenance inconnue</t>
   </si>
   <si>
     <t>PAT-001</t>
